--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487668_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487668_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2765</v>
+        <v>5.2941</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3463</v>
+        <v>5.2277</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0699</v>
+        <v>0.0664</v>
       </c>
       <c r="G2" t="n">
         <v>2.6263</v>
@@ -610,13 +610,13 @@
         <v>2.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8681</v>
+        <v>0.8858</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5545</v>
+        <v>1.4359</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6864</v>
+        <v>-0.5501</v>
       </c>
       <c r="V2" t="n">
         <v>1.0059</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5236</v>
+        <v>3.0241</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7705</v>
+        <v>1.271</v>
       </c>
       <c r="F3" t="n">
         <v>1.7531</v>
@@ -688,10 +688,10 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5944</v>
+        <v>-0.0939</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2299</v>
+        <v>0.2706</v>
       </c>
       <c r="U3" t="n">
         <v>-0.3645</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.147</v>
+        <v>1.9739</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8592</v>
+        <v>2.7406</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7667</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3198</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0489</v>
+        <v>-0.1242</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0134</v>
+        <v>-0.1052</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0355</v>
+        <v>-0.0191</v>
       </c>
       <c r="V4" t="n">
         <v>1.8358</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6878</v>
+        <v>0.4804</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7212</v>
+        <v>1.541</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0334</v>
+        <v>-1.0607</v>
       </c>
       <c r="G5" t="n">
         <v>-0.65</v>
@@ -844,13 +844,13 @@
         <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9109</v>
+        <v>0.7035</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2577</v>
+        <v>1.0775</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3468</v>
+        <v>-0.374</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3194</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4364</v>
+        <v>-0.4214</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2084</v>
+        <v>-0.2479</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.228</v>
+        <v>-0.1735</v>
       </c>
       <c r="G6" t="n">
         <v>0.0935</v>
@@ -922,13 +922,13 @@
         <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1462</v>
+        <v>0.1612</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0863</v>
+        <v>0.0468</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0599</v>
+        <v>0.1144</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0642</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. REAL BERMUDEZ</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7804</v>
+        <v>-0.5625</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7082000000000001</v>
+        <v>0.0926</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0722</v>
+        <v>-0.6551</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1129</v>
+        <v>-1.2687</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1541</v>
+        <v>-1.8488</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2669</v>
+        <v>0.58</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0206</v>
+        <v>-0.2389</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6673</v>
+        <v>-0.0762</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5339</v>
+        <v>-0.9537</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1335</v>
+        <v>-1.6099</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4004</v>
+        <v>0.6562</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7761</v>
+        <v>2.1344</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3881</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1086</v>
+        <v>0.2002</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1211</v>
+        <v>0.4077</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2297</v>
+        <v>-0.2075</v>
       </c>
       <c r="V7" t="n">
+        <v>-1.6283</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.2239</v>
-      </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>A. REAL BERMUDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.005</v>
+        <v>-0.8438</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3499</v>
+        <v>-0.6081</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6551</v>
+        <v>-0.2358</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2687</v>
+        <v>-0.1129</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8488</v>
+        <v>0.1541</v>
       </c>
       <c r="I8" t="n">
-        <v>0.58</v>
+        <v>-0.2669</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3151</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2389</v>
+        <v>0.0206</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0762</v>
+        <v>-0.6673</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9537</v>
+        <v>0.5339</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6099</v>
+        <v>0.1335</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6562</v>
+        <v>0.4004</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1344</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q8" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.1344</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.2423</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.0348</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.2075</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.6283</v>
-      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6283</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3709</v>
+        <v>-1.9261</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.658</v>
+        <v>-2.1044</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7128</v>
+        <v>0.1783</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-4.011</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3083</v>
+        <v>-2.7575</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5689</v>
+        <v>-1.2535</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4525</v>
+        <v>-2.4454</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4119</v>
+        <v>-1.0751</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0406</v>
+        <v>-1.3702</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.192</v>
+        <v>-1.5656</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7202</v>
+        <v>-1.6824</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5283</v>
+        <v>0.1168</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5523</v>
+        <v>2.5224</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3582</v>
+        <v>2.5224</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6911</v>
+        <v>-0.3152</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.424</v>
+        <v>0.3409</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2672</v>
+        <v>-0.6561</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6119</v>
+        <v>-0.1224</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6119</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7127</v>
+        <v>-1.9671</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6124</v>
+        <v>-3.0303</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8997000000000001</v>
+        <v>1.0632</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5113</v>
@@ -1234,13 +1234,13 @@
         <v>2.7164</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4432</v>
+        <v>-0.6976</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7874</v>
+        <v>-0.2053</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6559</v>
+        <v>-0.4923</v>
       </c>
       <c r="V10" t="n">
         <v>0.6597</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0782</v>
+        <v>-2.0616</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1475</v>
+        <v>-1.4578</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0693</v>
+        <v>-0.6038</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.011</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7575</v>
+        <v>-1.3083</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2535</v>
+        <v>0.5689</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4454</v>
+        <v>0.4525</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0751</v>
+        <v>0.4119</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3702</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5656</v>
+        <v>-1.192</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6824</v>
+        <v>-1.7202</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1168</v>
+        <v>0.5283</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5224</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4672</v>
+        <v>-0.3819</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.2238</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7651</v>
+        <v>-0.1581</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1224</v>
+        <v>0.6119</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1224</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.593</v>
+        <v>-6.8174</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5177</v>
+        <v>-5.415</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0753</v>
+        <v>-1.4024</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0453</v>
@@ -1390,13 +1390,13 @@
         <v>2.5224</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8733</v>
+        <v>0.6488</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.6264</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3495</v>
+        <v>0.0225</v>
       </c>
       <c r="V12" t="n">
         <v>1.1015</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.341699999999999</v>
+        <v>-3.827399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.504899999999999</v>
+        <v>-1.990599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8368</v>
+        <v>-1.837</v>
       </c>
       <c r="G13" t="n">
         <v>-10.7907</v>
@@ -1441,7 +1441,7 @@
         <v>-2.725000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.327700000000002</v>
+        <v>1.327700000000001</v>
       </c>
       <c r="K13" t="n">
         <v>7.2502</v>
@@ -1459,7 +1459,7 @@
         <v>3.1976</v>
       </c>
       <c r="P13" t="n">
-        <v>4.850899999999999</v>
+        <v>4.850900000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.463</v>
@@ -1468,13 +1468,13 @@
         <v>22.3137</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4822000000000002</v>
+        <v>1.0318</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1363</v>
+        <v>3.6505</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.6188</v>
+        <v>-2.6186</v>
       </c>
       <c r="V13" t="n">
         <v>1.0805</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0156</v>
+        <v>2.7081</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3645</v>
+        <v>0.5194</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6511</v>
+        <v>2.1888</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8847</v>
+        <v>1.1407</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1541</v>
+        <v>3.4158</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0388</v>
+        <v>-2.275</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7361</v>
+        <v>1.2821</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08649999999999999</v>
+        <v>3.9464</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6495</v>
+        <v>-2.6643</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1487</v>
+        <v>-0.1413</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2406</v>
+        <v>-0.5306</v>
       </c>
       <c r="O14" t="n">
         <v>0.3893</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R14" t="n">
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1592</v>
+        <v>0.2092</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1971</v>
+        <v>0.2075</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0379</v>
+        <v>0.0017</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5537</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3418</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3273</v>
+        <v>2.7054</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8108</v>
+        <v>2.1633</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5165</v>
+        <v>0.5421</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6138</v>
+        <v>0.8847</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9847</v>
+        <v>-0.1541</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3709</v>
+        <v>1.0388</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7089</v>
+        <v>0.7361</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6683</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0406</v>
+        <v>0.6495</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.1487</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3164</v>
+        <v>-0.2406</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4115</v>
+        <v>0.3893</v>
       </c>
       <c r="P15" t="n">
         <v>-0.5821</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3582</v>
+        <v>2.3284</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0718</v>
+        <v>0.849</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1817</v>
+        <v>0.9959</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2535</v>
+        <v>-0.1469</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2239</v>
+        <v>1.5537</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>3.3418</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5831</v>
+        <v>2.255</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2814</v>
+        <v>1.011</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8645</v>
+        <v>1.244</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1407</v>
+        <v>1.6138</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4158</v>
+        <v>1.9847</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.275</v>
+        <v>-0.3709</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2821</v>
+        <v>1.7089</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9464</v>
+        <v>1.6683</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.6643</v>
+        <v>0.0406</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1413</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5306</v>
+        <v>0.3164</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3893</v>
+        <v>-0.4115</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.5821</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.3582</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.3284</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.9159</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5933</v>
+        <v>0.0185</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3225</v>
+        <v>-0.0191</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0396</v>
+        <v>1.3272</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.862</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7014</v>
+        <v>2.1892</v>
       </c>
       <c r="G17" t="n">
         <v>0.7243000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>2.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6736</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9959</v>
+        <v>0.7957</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3223</v>
+        <v>0.1655</v>
       </c>
       <c r="V17" t="n">
         <v>0.6119</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.069</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2425</v>
+        <v>-0.8869</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3358</v>
+        <v>1.9559</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7253</v>
+        <v>1.8424</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9334</v>
+        <v>0.8848</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7918</v>
+        <v>0.9576</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3881</v>
+        <v>2.4857</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7919</v>
+        <v>2.9907</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5962</v>
+        <v>-0.5049</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3371</v>
+        <v>-0.6433</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8585</v>
+        <v>-2.1058</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1956</v>
+        <v>1.4626</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9702</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1021</v>
+        <v>0.3696</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5709</v>
+        <v>0.226</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4688</v>
+        <v>0.1436</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9504</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1743</v>
+        <v>0.3212</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7955</v>
+        <v>0.9707</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0871</v>
+        <v>2.0423</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8825</v>
+        <v>-1.0717</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8424</v>
+        <v>2.7253</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8848</v>
+        <v>0.9334</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9576</v>
+        <v>1.7918</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4857</v>
+        <v>2.3881</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9907</v>
+        <v>1.7919</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5049</v>
+        <v>0.5962</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6433</v>
+        <v>0.3371</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1058</v>
+        <v>-0.8585</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4626</v>
+        <v>1.1956</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7463</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.096</v>
+        <v>0.166</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0258</v>
+        <v>0.3707</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0703</v>
+        <v>-0.2047</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6032999999999999</v>
+        <v>-0.9504</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3212</v>
+        <v>-2.1743</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1117</v>
+        <v>0.9515</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7261</v>
+        <v>1.0264</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>2.7777</v>
@@ -2014,13 +2014,13 @@
         <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1036</v>
+        <v>-0.2638</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6662</v>
+        <v>-0.3659</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4374</v>
+        <v>0.1021</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5624</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4211</v>
+        <v>-0.4883</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5695</v>
+        <v>-0.5706</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9906</v>
+        <v>0.0823</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6924</v>
+        <v>-0.2064</v>
       </c>
       <c r="H21" t="n">
-        <v>1.118</v>
+        <v>-0.8321</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5745</v>
+        <v>0.6257</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7501</v>
+        <v>0.3814</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7095</v>
+        <v>1.0793</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0406</v>
+        <v>-0.6979</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0577</v>
+        <v>-0.5879</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5916</v>
+        <v>-1.9114</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5339</v>
+        <v>1.3235</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>2.3284</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0608</v>
+        <v>-0.1792</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7896</v>
+        <v>0.1988</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2712</v>
+        <v>-0.3779</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.7862</v>
+        <v>1.4495</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7862</v>
+        <v>-1.2803</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1875</v>
+        <v>-1.0329</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.849</v>
+        <v>-0.7489</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3385</v>
+        <v>-0.284</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2669</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2788</v>
+        <v>-0.1242</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2239</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7127</v>
+        <v>-1.1546</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5259</v>
+        <v>0.8688</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8132</v>
+        <v>-2.0235</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1373</v>
+        <v>1.6924</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4317</v>
+        <v>1.118</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7056</v>
+        <v>0.5745</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9202</v>
+        <v>1.7501</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6261</v>
+        <v>1.7095</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2941</v>
+        <v>0.0406</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2171</v>
+        <v>-0.0577</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1944</v>
+        <v>-0.5916</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4115</v>
+        <v>0.5339</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4246</v>
+        <v>0.3272</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3645</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0601</v>
+        <v>0.2384</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.7862</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.7862</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1167</v>
+        <v>-1.9674</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4715</v>
+        <v>-2.7261</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6452</v>
+        <v>0.7587</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2064</v>
+        <v>-2.1373</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8321</v>
+        <v>-0.4317</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6257</v>
+        <v>-1.7056</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3814</v>
+        <v>-1.9202</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0793</v>
+        <v>-0.6261</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6979</v>
+        <v>-1.2941</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5879</v>
+        <v>-0.2171</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9114</v>
+        <v>0.1944</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3235</v>
+        <v>-0.4115</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5523</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3284</v>
+        <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8075</v>
+        <v>0.1699</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.1643</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1054</v>
+        <v>0.0056</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4495</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.3416</v>
+        <v>7.3437</v>
       </c>
       <c r="E25" t="n">
-        <v>1.836699999999999</v>
+        <v>1.8367</v>
       </c>
       <c r="F25" t="n">
-        <v>3.504700000000001</v>
+        <v>5.506900000000001</v>
       </c>
       <c r="G25" t="n">
         <v>10.7907</v>
       </c>
       <c r="H25" t="n">
-        <v>8.065600000000002</v>
+        <v>8.0656</v>
       </c>
       <c r="I25" t="n">
-        <v>2.725099999999999</v>
+        <v>2.725100000000001</v>
       </c>
       <c r="J25" t="n">
         <v>12.1184</v>
@@ -2395,7 +2395,7 @@
         <v>5.922599999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.851</v>
+        <v>-4.850999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-22.3137</v>
@@ -2404,13 +2404,13 @@
         <v>17.4631</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4822999999999995</v>
+        <v>2.4843</v>
       </c>
       <c r="T25" t="n">
-        <v>2.618799999999999</v>
+        <v>2.6188</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.1363</v>
+        <v>-0.1343</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0806</v>
